--- a/FR752_V06.X/FR752解析_20260826.xlsx
+++ b/FR752_V06.X/FR752解析_20260826.xlsx
@@ -9,18 +9,19 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="3" r:id="rId1"/>
     <sheet name="工作表2" sheetId="2" r:id="rId2"/>
+    <sheet name="工作表3" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30434" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30442" uniqueCount="247">
   <si>
     <t>B0</t>
   </si>
@@ -1078,6 +1079,30 @@
     <t>狀態</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>廠內編號</t>
+  </si>
+  <si>
+    <t>FR752-B101</t>
+  </si>
+  <si>
+    <t>車型</t>
+  </si>
+  <si>
+    <t>2024 ford F-150 XLT</t>
+  </si>
+  <si>
+    <t>信號</t>
+  </si>
+  <si>
+    <t>LIN</t>
+  </si>
+  <si>
+    <t>頻率</t>
+  </si>
 </sst>
 </file>
 
@@ -1214,7 +1239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1279,6 +1304,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -96309,4 +96337,141 @@
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="24">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="24">
+        <v>2</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="24">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="24">
+        <v>4</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="C5" s="24">
+        <v>10417</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="24">
+        <v>5</v>
+      </c>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="24">
+        <v>6</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="24">
+        <v>7</v>
+      </c>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="24">
+        <v>8</v>
+      </c>
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="24">
+        <v>9</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="24">
+        <v>10</v>
+      </c>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="24">
+        <v>11</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="24">
+        <v>12</v>
+      </c>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="24">
+        <v>13</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="24">
+        <v>14</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>